--- a/artfynd/A 19628-2025 artfynd.xlsx
+++ b/artfynd/A 19628-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19628-2025 artfynd.xlsx
+++ b/artfynd/A 19628-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
